--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92328</v>
+        <v>92484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92546</v>
+        <v>92554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92562</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92564</v>
+        <v>92568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20953-2025 artfynd.xlsx
+++ b/artfynd/A 20953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825239</v>
       </c>
       <c r="B2" t="n">
-        <v>92568</v>
+        <v>92571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
